--- a/companies.xlsx
+++ b/companies.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="196">
   <si>
     <t>Company Name</t>
   </si>
@@ -485,6 +485,123 @@
   </si>
   <si>
     <t>data:image/jpeg;base64,/9j/4AAQSkZJRgABAQAAAQABAAD/2wCEAAkGBxIHBhIPEA8SDQ8QFRAQFw8QEBYPEBYTFRcWGRUWFhUYHSgjGBonGxMTIT0hJikrMC4uFx81ODMsNygtLisBCgoKDg0OGxAQGzYlICYwLS0wKy0rLSs3Ky0tLS0tLS0vLy0vLS0tLS0tLS0tLS0tLS0tLS0tLS0tLSstLS0tLf/AABEIAMIBAwMBEQACEQEDEQH/xAAbAAEAAgMBAQAAAAAAAAAAAAAAAQYEBQcDAv/EADcQAAIBAwIDBQYFAgcAAAAAAAABAgMEEQUGEiExEyJBUWEHQnGBkaEUFSMyYnKxFzNDVIKS0f/EABsBAQACAwEBAAAAAAAAAAAAAAABBQMEBgIH/8QALxEBAAICAQMDAgQFBQAAAAAAAAECAwQREiExBRNRQWEicYGRBhUyQqEjNLHR8P/aAAwDAQACEQMRAD8A7iAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABDAEAgJJAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAIYESlwo8zbgaTbGrPUYVVJ9+E5cv45wv7GHBl64lq62Xr5iflvTYbQAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAEMDU69cO3dNrpxZfr6FP6ps3wdMx4betijJzEqPXrT0TW3Upvk3xrylGTy0/uvkeMWXji9J7OczVvrZpjwuVPdVt+WOvOoqSXJwb73F5JeJaU2KWrzyudKmTbnjFXmVP1P2l1K1TgtaGM8lKfeb+CXQxTtTzxWHUYv4eitevNfj5jjw9bHd91a1k72va20Xh9nN/qtekUzcxYNi8czWf2Ve7TSx9sduZ+YlbNL3bZarW7OjcwnUfSGcSfwMt8GSveYVMWifDdNmKB8OtGPWcV80TxPw8TkpXzKFXi/fj9UJrJ7tJ8S9FLJEwyRKHNLxSEd0TaI8inl9c/MTEnVEz2S5Y9ATxCO0XmvqOJR1x8naLzX1HBNo+TtF5r6jiTrr8naLzX1ExJ11+Up5XmEx3hOQlIAAAAAAAAAAAAAAEMDA1i0/FWbxzlHvIrfU9WdjBMR5+jY1cnt5OZUrULf8Vb8PvRzw58/L4HJ625bFPTfw3N707HtRE+J+Yhzy+7SV64VE1NPHB/4dFS9LV6q+HVaOtq6Gv1144iO9+O8/nwx9RnX0mKcUoKX+rHnJemfdOg9Ipr5I5nvb448OT9S9fnctNMM8R8xM9/3WDYvs9nryVzduVK3k8qPSpU9fSPqWextVxx008/8KmsTPld9V1Oz2hFUbW2pusl0ikuH1lLq2auOmXL/AFTPCv3PUKYPw1jmfhpNPutQ3XdOMarhTX7nHuQS8uXVma0YcUcTHMq3Fk2du/4ZmI+0rBD2f05rNS4qVJefRGvOzE/2w3/5XaZ5nLLwufZ5FLNK5mn5SXL6omNus/2wi3pduO2SVws6KsNPhBy5U4pOTfkubbNW0za09lpSvRSItPiPLmW59XqaxqFSpb8UaNCOHNPCaT/cyywY6Ur038uc3NnLmv1YvEdu0sXaurVKO4KLnUk4OXC022nxLC+7PWbFWaTxDDp7eSuWOq0zzPDou4NIravOMI1+wox5vhWZyl6+hXYslad+OXQ7OC+biItNePj6udbmpz0bUuxhc1KrSTbfdw34cixw9OSvM1hz+5N8F+mMkyytp6XW3BUnm4qUoQS7yfFlvw5nnPamL+2JZdDHm2Znm8xEfVZKeg/kNKtc1riVeEIS4U3jm1jL+prTljLMVisQso1p14te15mOJ8ud/j60nhVJ5fhxMsPbpEc8OejPmmeOqf3dn0G0dlpFKnJuUlFcTby3J9SnyTE3nh12rW1cNYt5bAx/VsCJEgAAAAAAAAAAAAAhg4aPc+5aW37VuTUqrXdpLq36+SMWXJFI5lvaOhk279NfH1lzbT93OrczdziMZNyU4rlH+JzO36fbPbrxR3n9HUbXp9MGLqpPj5V3V92u51VVIU0qMMxWV35LzbOr0f4driw8ZJnq+OYmHG721kz16KzxX85j92/oyVajCbhmEsTUakevxTKa3VhyTWJ4mPif+nO2rfDbu6no+prUNG7SEUpRi1wJclJLkkvItMOX3IiZ/Vb48vXj6o8uMXlWVW8nKeXOUpN565ydFSIiI4cbltNrzM/Lqvs7jBbbjwYy5T4sdeL1Kvb75HTekxX2O3zL13vqstJ0hTpz4Krkox5Zz5/bJGtj9y8xLJ6hsTgxxMeVS0Hct7qer0qKq8pS5vhXKK6m1m18dKzKq1N/PlzVq2G+twSuav4G2zNv/McObePcWPuY9bFEfjuz+pbc2n2Mf6/ox9Mm4aJKyhp9ZOrGSnVlhc8dW8ckTeJm/VMvGvaPZnFWO/lSKdR0aqkusGpfNPJvzETVSY7dNol3O1u1PTI1m+Tgpt/LmUk0nr6Xa0yxOL3Pty4pq169Q1KpWfvyk/gvBFzjp0xEQ47Zv7mW1vmXVNiaf+X7ehlYnU/Ufz6fbBVbN+u/Lp/TsPtYI+/dq/abqHY6bC3T51XxNfwj4fXBm06fimzV9YzdNIpCn7M0/wDMdwU4tZjB9pLy7vNI29i/TT81ToYvcz1+3d2bBTuwGBKAAAAAAAAAAAACAICO7R7gtb+4WLSvSpRfXji3L5SXQx5ItP8ASsNS+nX/AHFZn8pcr1vTqemXUne3jqVk8uFOM5zf/KSS+5GH03Jmn8UxwurfxDgw1imCk/rEK9WVbW6ypWttU7PPKCTk36zmX2vq4dWO3n8+XO7m/n3L85J7faOF4217Lp0aKr3TUqq70bdc4r+p+L9Cr9X2suTFNdft88/H2YteK1tzf/DfVLaNb9KouHwzjnF+B8/08tsWfov9e3/uVnvatNnB28x3hk7IhO01CvQlyxzfllcuX1Os05nm0fRzOnE1taksjX9kUdUqupCToVJc20sxb88eBc4du1I4nw8bXplMs9VfLT2mzr7S6jdvcwin4cUo5+KwZbbOLJH4olqY/TtnDPOO0f5fWo7V1DV+FV69JqPRcT+vQU2MWP8ApiTLo7ebjrtHZl6JsuppcaklWiq04OnGajlRT6v4nnLsVvPLLr+m5MfVMzHMs/a+1fyS7nUlUVaU1jia7y8zHm2IvHENjT0Zw2m1vqsrWUa3Kx4iVCufZ06tzOSuOFSk2lwdE/A3q7kVhQ39HmbTMS31HQqtPbcrJ108pwVTh5qD8PiYLZazk6m/XVyRr+zzHjhXP8N5f7lf9DZndrH0V38mt8x+6/2lN0rWEXzcYxjlclyWDQtPM8r7HXprEKtuXaE9c1LtXccEVFRjDhzjHX6mzh2Yx14Vm76fbYydXL32ntZ7fupz7RVVOKj+3DWHnqRmz+5EPejo217TMz5Wg1lmAAAAAAAAAAAAAAgABHiEfm8a9pTuH36cJ/1QUv7iJmEvqjQhbrEIRgv4xUV9hMyPQiENLr9ipQ7WK7y6+q8yi9W0Ytxmr5jy39TPMT0Sy9Oso0pOt79SME/kiz0a/wChWbeZho3xxXLaY+ss9m1wJAEgQBIACAJQD7gEgACQAAAAAAAAAAAAAAAAHBgAAAAfNSCqQaayn4Hm1YtHEwmJmJ5hKWFgmKxEcQhOCTgAAAADAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAP//Z</t>
+  </si>
+  <si>
+    <t>WMS System</t>
+  </si>
+  <si>
+    <t>Official Website</t>
+  </si>
+  <si>
+    <t>Company Type</t>
+  </si>
+  <si>
+    <t>Countries of Operation</t>
+  </si>
+  <si>
+    <t>Cloud Platform</t>
+  </si>
+  <si>
+    <t>Warehouse Automation</t>
+  </si>
+  <si>
+    <t>Tracking Platform</t>
+  </si>
+  <si>
+    <t>Sustainability Initiatives</t>
+  </si>
+  <si>
+    <t>Source URL</t>
+  </si>
+  <si>
+    <t>In-house WMS</t>
+  </si>
+  <si>
+    <t>https://www.delhivery.com</t>
+  </si>
+  <si>
+    <t>Public</t>
+  </si>
+  <si>
+    <t>India</t>
+  </si>
+  <si>
+    <t>AWS</t>
+  </si>
+  <si>
+    <t>Automated Sort Centers</t>
+  </si>
+  <si>
+    <t>Delhivery One</t>
+  </si>
+  <si>
+    <t>EV adoption, network optimization</t>
+  </si>
+  <si>
+    <t>https://www.delhivery.com/about-us</t>
+  </si>
+  <si>
+    <t>SAP EWM</t>
+  </si>
+  <si>
+    <t>https://www.bluedart.com</t>
+  </si>
+  <si>
+    <t>Microsoft Azure</t>
+  </si>
+  <si>
+    <t>Automated Hubs</t>
+  </si>
+  <si>
+    <t>TrackDart</t>
+  </si>
+  <si>
+    <t>Green logistics initiatives</t>
+  </si>
+  <si>
+    <t>DTDC WMS</t>
+  </si>
+  <si>
+    <t>https://www.dtdc.com</t>
+  </si>
+  <si>
+    <t>Private</t>
+  </si>
+  <si>
+    <t>India &amp; International</t>
+  </si>
+  <si>
+    <t>Automated Sorting</t>
+  </si>
+  <si>
+    <t>DTDC Tracking</t>
+  </si>
+  <si>
+    <t>Sustainable packaging</t>
+  </si>
+  <si>
+    <t>https://www.shadowfax.in</t>
+  </si>
+  <si>
+    <t>AI-enabled hubs</t>
+  </si>
+  <si>
+    <t>Shadowfax Tracking</t>
+  </si>
+  <si>
+    <t>EV delivery initiatives</t>
+  </si>
+  <si>
+    <t>https://www.mahindralogistics.com</t>
+  </si>
+  <si>
+    <t>Automated Warehouses</t>
+  </si>
+  <si>
+    <t>MLL Tracking</t>
+  </si>
+  <si>
+    <t>Green logistics</t>
   </si>
 </sst>
 </file>
@@ -821,7 +938,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:AE11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="16.7265625" customWidth="1"/>
@@ -848,7 +965,7 @@
     <col min="23" max="23" width="142.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -915,8 +1032,35 @@
       <c r="V1" t="s">
         <v>146</v>
       </c>
+      <c r="W1" t="s">
+        <v>157</v>
+      </c>
+      <c r="X1" t="s">
+        <v>158</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>159</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>160</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>161</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>162</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>163</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>164</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>165</v>
+      </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>21</v>
       </c>
@@ -983,8 +1127,35 @@
       <c r="V2" t="s">
         <v>147</v>
       </c>
+      <c r="W2" t="s">
+        <v>166</v>
+      </c>
+      <c r="X2" t="s">
+        <v>167</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>168</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>169</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>170</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>171</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>172</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>173</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>174</v>
+      </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>40</v>
       </c>
@@ -1051,8 +1222,35 @@
       <c r="V3" t="s">
         <v>148</v>
       </c>
+      <c r="W3" t="s">
+        <v>175</v>
+      </c>
+      <c r="X3" t="s">
+        <v>176</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>168</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>169</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>178</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>179</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>180</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>176</v>
+      </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>54</v>
       </c>
@@ -1119,8 +1317,35 @@
       <c r="V4" t="s">
         <v>149</v>
       </c>
+      <c r="W4" t="s">
+        <v>181</v>
+      </c>
+      <c r="X4" t="s">
+        <v>182</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>183</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>184</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>170</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>185</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>186</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>187</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>182</v>
+      </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>68</v>
       </c>
@@ -1188,7 +1413,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>79</v>
       </c>
@@ -1255,8 +1480,35 @@
       <c r="V6" t="s">
         <v>151</v>
       </c>
+      <c r="W6" t="s">
+        <v>166</v>
+      </c>
+      <c r="X6" t="s">
+        <v>188</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>183</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>169</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>170</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>189</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>190</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>191</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>188</v>
+      </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>92</v>
       </c>
@@ -1324,7 +1576,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>102</v>
       </c>
@@ -1391,8 +1643,35 @@
       <c r="V8" t="s">
         <v>153</v>
       </c>
+      <c r="W8" t="s">
+        <v>175</v>
+      </c>
+      <c r="X8" t="s">
+        <v>192</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>168</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>169</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>177</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>193</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>194</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>195</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>192</v>
+      </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>114</v>
       </c>
@@ -1460,7 +1739,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>126</v>
       </c>
@@ -1528,7 +1807,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>137</v>
       </c>
